--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N10_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,38 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>group</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>W0029F0002T0006Z000C1N10.png</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>8.801881597522645</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8.719377896575658</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>T7604</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>G5</t>
         </is>
       </c>
     </row>

--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N10_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.801881597522645</v>
+        <v>1.43030575959743</v>
       </c>
       <c r="D2" t="n">
-        <v>8.719377896575658</v>
+        <v>1.416898908193544</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
